--- a/05-results/bacterial_mapping/DeSeq2_Significant_taxa_comparisons_c0.001.xlsx
+++ b/05-results/bacterial_mapping/DeSeq2_Significant_taxa_comparisons_c0.001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meriamvanos/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193D000F-545D-7944-A4A2-3FBBB0061BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534D52B3-3553-254D-9A11-2C9480EE5CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{8012F023-DEB5-4909-81FF-4A276A7F076A}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{8012F023-DEB5-4909-81FF-4A276A7F076A}"/>
   </bookViews>
   <sheets>
     <sheet name="Kk2_North_vs_South_c0.001" sheetId="5" r:id="rId1"/>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="27" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5">
         <v>1935446</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>166935</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="29" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="13">
         <v>2961941</v>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="30" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="13">
         <v>29484</v>
@@ -2537,7 +2537,7 @@
     </row>
     <row r="31" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5">
         <v>2708346</v>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>521720</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>2038776</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="34" spans="1:13" s="30" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="30">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" s="30">
         <v>2600598</v>
